--- a/Packages/cn.etetet.startconfig/Excel/StartConfig/Example/StartMachineConfig@s.xlsx
+++ b/Packages/cn.etetet.startconfig/Excel/StartConfig/Example/StartMachineConfig@s.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Unity\ET\ET9.0\Packages\cn.etetet.startconfig\Excel\StartConfig\Example\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Unity\ET\ET9.0_YIUIMorallyEnlightenedPerson\Packages\cn.etetet.startconfig\Excel\StartConfig\Example\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CB305520-6CFF-4376-A427-6A12736DA1C0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{342F35FE-6BC6-45C9-AEE2-81F6C3AEC9E7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1950" yWindow="1950" windowWidth="38700" windowHeight="15345" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="11">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="10">
   <si>
     <t>Id</t>
   </si>
@@ -49,11 +49,7 @@
     <t>string</t>
   </si>
   <si>
-    <t>192.168.2.159</t>
-  </si>
-  <si>
-    <t>192.168.2.159</t>
-    <phoneticPr fontId="3" type="noConversion"/>
+    <t>127.0.0.1</t>
   </si>
 </sst>
 </file>
@@ -500,7 +496,7 @@
         <v>1</v>
       </c>
       <c r="D6" s="6" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E6" s="5" t="s">
         <v>9</v>
